--- a/backend/implant_library_latest.xlsx
+++ b/backend/implant_library_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhijit/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C834964E-79B8-E143-AF3C-99D7395BE7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C321EE7-DDD0-4641-A810-15484EE65648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="80" yWindow="580" windowWidth="25520" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Length_mm</t>
-  </si>
-  <si>
-    <t>Cowellmedi INNO Submerged Narrow</t>
   </si>
   <si>
     <t>Noble Biocare</t>
@@ -184,9 +181,6 @@
     <t xml:space="preserve">Alpha Bio </t>
   </si>
   <si>
-    <t>Bio SPI</t>
-  </si>
-  <si>
     <t>Blue Sky Bio</t>
   </si>
   <si>
@@ -218,6 +212,12 @@
   </si>
   <si>
     <t>Implant System</t>
+  </si>
+  <si>
+    <t>SPI</t>
+  </si>
+  <si>
+    <t>BSPI</t>
   </si>
 </sst>
 </file>
@@ -605,10 +605,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -619,10 +619,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -633,10 +633,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -647,10 +647,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -661,10 +661,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -675,10 +675,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -689,10 +689,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -703,10 +703,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -717,10 +717,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -745,10 +745,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>4.3</v>
@@ -773,10 +773,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>4.3</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>4.3</v>
@@ -801,10 +801,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>4.3</v>
@@ -815,10 +815,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>4.3</v>
@@ -829,10 +829,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>4.3</v>
@@ -843,10 +843,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -857,10 +857,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -871,10 +871,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -927,10 +927,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>5.5</v>
@@ -941,10 +941,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -955,10 +955,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>5.5</v>
@@ -969,10 +969,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>5.5</v>
@@ -983,10 +983,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>5.5</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>3.75</v>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>3.75</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>3.75</v>
@@ -1053,10 +1053,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33">
         <v>3.75</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>3.75</v>
@@ -1081,10 +1081,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>3.75</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36">
         <v>3.75</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>4.3</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>4.3</v>
@@ -1137,10 +1137,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>4.3</v>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>4.3</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>4.3</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>4.3</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>4.3</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -1249,10 +1249,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -1263,10 +1263,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C48">
         <v>5</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>5</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
         <v>5</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
         <v>3</v>
-      </c>
-      <c r="B51" t="s">
-        <v>4</v>
       </c>
       <c r="C51">
         <v>5.5</v>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
         <v>3</v>
-      </c>
-      <c r="B52" t="s">
-        <v>4</v>
       </c>
       <c r="C52">
         <v>5.5</v>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
         <v>3</v>
-      </c>
-      <c r="B53" t="s">
-        <v>4</v>
       </c>
       <c r="C53">
         <v>5.5</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54" t="s">
         <v>3</v>
-      </c>
-      <c r="B54" t="s">
-        <v>4</v>
       </c>
       <c r="C54">
         <v>5.5</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
         <v>3</v>
-      </c>
-      <c r="B55" t="s">
-        <v>4</v>
       </c>
       <c r="C55">
         <v>5.5</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56" t="s">
         <v>3</v>
-      </c>
-      <c r="B56" t="s">
-        <v>4</v>
       </c>
       <c r="C56">
         <v>5.5</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57">
         <v>3.3</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="s">
         <v>12</v>
-      </c>
-      <c r="B58" t="s">
-        <v>13</v>
       </c>
       <c r="C58">
         <v>4.0999999999999996</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
         <v>12</v>
-      </c>
-      <c r="B59" t="s">
-        <v>13</v>
       </c>
       <c r="C59">
         <v>4.8</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
         <v>12</v>
-      </c>
-      <c r="B60" t="s">
-        <v>13</v>
       </c>
       <c r="C60">
         <v>6.5</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" t="s">
         <v>14</v>
-      </c>
-      <c r="B61" t="s">
-        <v>15</v>
       </c>
       <c r="C61">
         <v>3.5</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" t="s">
         <v>14</v>
-      </c>
-      <c r="B62" t="s">
-        <v>15</v>
       </c>
       <c r="C62">
         <v>3.75</v>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
         <v>14</v>
-      </c>
-      <c r="B63" t="s">
-        <v>15</v>
       </c>
       <c r="C63">
         <v>4</v>
@@ -1487,10 +1487,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
         <v>14</v>
-      </c>
-      <c r="B64" t="s">
-        <v>15</v>
       </c>
       <c r="C64">
         <v>4</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>13</v>
+      </c>
+      <c r="B65" t="s">
         <v>14</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
       </c>
       <c r="C65">
         <v>5</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>13</v>
+      </c>
+      <c r="B66" t="s">
         <v>14</v>
-      </c>
-      <c r="B66" t="s">
-        <v>15</v>
       </c>
       <c r="C66">
         <v>6</v>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C67" s="2">
         <v>3.5</v>
@@ -1543,10 +1543,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C68" s="2">
         <v>3.75</v>
@@ -1557,10 +1557,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C69" s="2">
         <v>4</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C70" s="2">
         <v>4</v>
@@ -1585,10 +1585,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C71" s="2">
         <v>5</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C72" s="2">
         <v>6</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2">
         <v>3.5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2">
         <v>3.5</v>
@@ -1641,10 +1641,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2">
         <v>4.3</v>
@@ -1655,10 +1655,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2">
         <v>4.3</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C77" s="2">
         <v>5</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C78" s="2">
         <v>5</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C79" s="2">
         <v>3.5</v>
@@ -1711,10 +1711,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2">
         <v>3.5</v>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81" s="2">
         <v>4.3</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C82" s="2">
         <v>4.3</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C83" s="2">
         <v>5</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C84" s="2">
         <v>5</v>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C85" s="2">
         <v>3.5</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C86" s="2">
         <v>3.5</v>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C87" s="2">
         <v>3.75</v>
@@ -1823,10 +1823,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C88" s="2">
         <v>3.75</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C89" s="2">
         <v>4</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C90" s="2">
         <v>4</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C91" s="2">
         <v>5</v>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C92" s="2">
         <v>3.5</v>
@@ -1893,10 +1893,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C93" s="2">
         <v>3.5</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C94" s="2">
         <v>3.75</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C95" s="2">
         <v>3.75</v>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C96" s="2">
         <v>4</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C97" s="2">
         <v>4</v>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C98" s="2">
         <v>5</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C99">
         <v>3.5</v>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>21</v>
+      </c>
+      <c r="B100" t="s">
         <v>22</v>
-      </c>
-      <c r="B100" t="s">
-        <v>23</v>
       </c>
       <c r="C100">
         <v>4</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B101" t="s">
         <v>22</v>
-      </c>
-      <c r="B101" t="s">
-        <v>23</v>
       </c>
       <c r="C101">
         <v>4.5</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C102">
         <v>5.5</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C103">
         <v>3.5</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C104">
         <v>4</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C105">
         <v>4.5</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C106">
         <v>3.5</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C108">
         <v>4.5</v>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C109">
         <v>5</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C110">
         <v>6</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" t="s">
         <v>26</v>
-      </c>
-      <c r="B111" t="s">
-        <v>27</v>
       </c>
       <c r="C111">
         <v>3.1</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B112" t="s">
         <v>26</v>
-      </c>
-      <c r="B112" t="s">
-        <v>27</v>
       </c>
       <c r="C112">
         <v>3.1</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B113" t="s">
         <v>26</v>
-      </c>
-      <c r="B113" t="s">
-        <v>27</v>
       </c>
       <c r="C113">
         <v>3.1</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B114" t="s">
         <v>26</v>
-      </c>
-      <c r="B114" t="s">
-        <v>2</v>
       </c>
       <c r="C114">
         <v>3.3</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C115">
         <v>3.5</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C116">
         <v>4</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C117">
         <v>4.5</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C118">
         <v>5</v>
@@ -2257,10 +2257,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" t="s">
         <v>29</v>
-      </c>
-      <c r="B119" t="s">
-        <v>30</v>
       </c>
       <c r="C119">
         <v>4</v>
@@ -2271,10 +2271,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" t="s">
         <v>29</v>
-      </c>
-      <c r="B120" t="s">
-        <v>30</v>
       </c>
       <c r="C120">
         <v>4</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>28</v>
+      </c>
+      <c r="B121" t="s">
         <v>29</v>
-      </c>
-      <c r="B121" t="s">
-        <v>30</v>
       </c>
       <c r="C121">
         <v>4.5</v>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
         <v>29</v>
-      </c>
-      <c r="B122" t="s">
-        <v>30</v>
       </c>
       <c r="C122">
         <v>5</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C123">
         <v>3.75</v>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C124">
         <v>3.75</v>
@@ -2341,10 +2341,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C125">
         <v>4</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C126">
         <v>4</v>
@@ -2369,10 +2369,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C127">
         <v>5.5</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B128" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C128">
         <v>5.5</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C129">
         <v>5.5</v>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B130" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C130">
         <v>6</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B131" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C131">
         <v>6</v>
@@ -2439,10 +2439,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B132" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C132">
         <v>3.5</v>
@@ -2453,10 +2453,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B133" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C133">
         <v>3.5</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B134" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C134">
         <v>3.5</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B135" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C135">
         <v>3.5</v>
@@ -2495,10 +2495,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B136" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C136">
         <v>3.5</v>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B137" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C137">
         <v>3.5</v>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C138" s="2">
         <v>4.5</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C139" s="2">
         <v>4.5</v>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C140" s="2">
         <v>4.5</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C141" s="2">
         <v>4.5</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C142" s="2">
         <v>4.5</v>
@@ -2593,10 +2593,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C143" s="2">
         <v>4.5</v>
@@ -2607,10 +2607,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C144" s="2">
         <v>5.5</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C145" s="2">
         <v>5.5</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C146" s="2">
         <v>5.5</v>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C147" s="2">
         <v>5.5</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C148" s="2">
         <v>5.5</v>
@@ -2677,10 +2677,10 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C149" s="2">
         <v>5.5</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C150" s="2">
         <v>7</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C151" s="2">
         <v>7</v>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C152" s="2">
         <v>7</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C153" s="2">
         <v>7</v>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C154" s="2">
         <v>7</v>
@@ -2761,10 +2761,10 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>33</v>
+      </c>
+      <c r="B155" t="s">
         <v>34</v>
-      </c>
-      <c r="B155" t="s">
-        <v>35</v>
       </c>
       <c r="C155">
         <v>3.7</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B156" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C156">
         <v>4.0999999999999996</v>
@@ -2789,10 +2789,10 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C157">
         <v>4.7</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B158" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C158">
         <v>3.8</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C159">
         <v>4.2</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B160" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C160">
         <v>4.5999999999999996</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B161" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C161">
         <v>4.5999999999999996</v>
@@ -2859,10 +2859,10 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B162" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C162">
         <v>5.2</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B163" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C163">
         <v>3</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B164" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C164">
         <v>3</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B165" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C165">
         <v>3</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B166" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C166">
         <v>3.4</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B167" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C167">
         <v>3.4</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B168" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C168">
         <v>3.4</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B169" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C169">
         <v>3.4</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B170" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C170">
         <v>4.5999999999999996</v>
@@ -2985,10 +2985,10 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B171" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C171">
         <v>4.5999999999999996</v>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B172" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C172">
         <v>5.8</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B173" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C173">
         <v>5.8</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>37</v>
+      </c>
+      <c r="B174" t="s">
         <v>38</v>
-      </c>
-      <c r="B174" t="s">
-        <v>39</v>
       </c>
       <c r="C174">
         <v>7</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>37</v>
+      </c>
+      <c r="B175" t="s">
         <v>38</v>
-      </c>
-      <c r="B175" t="s">
-        <v>39</v>
       </c>
       <c r="C175">
         <v>7</v>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>37</v>
+      </c>
+      <c r="B176" t="s">
         <v>38</v>
-      </c>
-      <c r="B176" t="s">
-        <v>39</v>
       </c>
       <c r="C176">
         <v>7</v>
@@ -3069,10 +3069,10 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>37</v>
+      </c>
+      <c r="B177" t="s">
         <v>38</v>
-      </c>
-      <c r="B177" t="s">
-        <v>39</v>
       </c>
       <c r="C177">
         <v>8</v>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
+        <v>37</v>
+      </c>
+      <c r="B178" t="s">
         <v>38</v>
-      </c>
-      <c r="B178" t="s">
-        <v>39</v>
       </c>
       <c r="C178">
         <v>8</v>
@@ -3097,10 +3097,10 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>37</v>
+      </c>
+      <c r="B179" t="s">
         <v>38</v>
-      </c>
-      <c r="B179" t="s">
-        <v>39</v>
       </c>
       <c r="C179">
         <v>8</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B180" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C180">
         <v>3.5</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B181" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C181">
         <v>4</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B182" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C182">
         <v>4.5</v>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B183" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C183">
         <v>5.5</v>
@@ -3167,10 +3167,10 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B184" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C184">
         <v>3</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B185" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C185">
         <v>3</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B186" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C186">
         <v>3</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B187" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C187">
         <v>3</v>
@@ -3223,10 +3223,10 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B188" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C188">
         <v>3</v>
@@ -3237,10 +3237,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B189" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C189">
         <v>3.5</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B190" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C190">
         <v>3.5</v>
@@ -3265,10 +3265,10 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B191" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C191">
         <v>3.5</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B192" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C192">
         <v>3.5</v>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B193" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C193">
         <v>3.5</v>
@@ -3307,10 +3307,10 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B194" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C194">
         <v>4</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B195" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C195">
         <v>4</v>
@@ -3335,10 +3335,10 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B196" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C196">
         <v>4</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B197" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C197">
         <v>4</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B198" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C198">
         <v>4</v>
@@ -3377,10 +3377,10 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B199" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C199">
         <v>4.5</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B200" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C200">
         <v>4.5</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B201" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C201">
         <v>4.5</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B202" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C202">
         <v>4.5</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B203" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C203">
         <v>4.5</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B204" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B205" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B206" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -3489,10 +3489,10 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B207" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B208" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -3517,10 +3517,10 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B209" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C209">
         <v>5.5</v>
@@ -3531,10 +3531,10 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B210" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C210">
         <v>5.5</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B211" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C211">
         <v>5.5</v>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B212" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C212">
         <v>5.5</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B213" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C213">
         <v>5.5</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B214" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C214">
         <v>6</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B215" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C215">
         <v>6</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B216" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C216">
         <v>6</v>
@@ -3629,10 +3629,10 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B217" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C217">
         <v>6</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B218" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C218">
         <v>6</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B219" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C219">
         <v>7</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B220" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C220">
         <v>7</v>
@@ -3685,10 +3685,10 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B221" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C221">
         <v>7</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B222" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C222">
         <v>7</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B223" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C223">
         <v>7</v>
@@ -3727,10 +3727,10 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B224" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C224">
         <v>4</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B225" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C225">
         <v>4</v>
@@ -3755,10 +3755,10 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B226" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C226">
         <v>4</v>
@@ -3769,10 +3769,10 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B227" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C227">
         <v>4</v>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B228" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C228">
         <v>4</v>
@@ -3797,10 +3797,10 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B229" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C229">
         <v>4.5</v>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B230" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C230">
         <v>4.5</v>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B231" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C231">
         <v>4.5</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B232" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C232">
         <v>4.5</v>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B233" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C233">
         <v>4.5</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B234" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C234">
         <v>5</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B235" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C235">
         <v>5</v>
@@ -3895,10 +3895,10 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B236" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C236">
         <v>5</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B237" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C237">
         <v>5</v>
@@ -3923,10 +3923,10 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B238" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C238">
         <v>5</v>
@@ -3937,10 +3937,10 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B239" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C239">
         <v>6</v>
@@ -3951,10 +3951,10 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B240" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C240">
         <v>6</v>
@@ -3965,10 +3965,10 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B241" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C241">
         <v>6</v>
@@ -3979,10 +3979,10 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B242" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C242">
         <v>6</v>
@@ -3993,10 +3993,10 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B243" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C243">
         <v>6</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B244" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C244">
         <v>7</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B245" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C245">
         <v>7</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B246" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C246">
         <v>7</v>
@@ -4049,10 +4049,10 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B247" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C247">
         <v>7</v>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B248" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C248">
         <v>7</v>
@@ -4077,10 +4077,10 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B249" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C249">
         <v>3.5</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B250" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C250">
         <v>3.5</v>
@@ -4105,10 +4105,10 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B251" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C251">
         <v>3.5</v>
@@ -4119,10 +4119,10 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B252" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C252">
         <v>3.5</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B253" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C253">
         <v>3.5</v>
@@ -4147,10 +4147,10 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B254" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C254">
         <v>3.5</v>
@@ -4161,10 +4161,10 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B255" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C255">
         <v>4</v>
@@ -4175,10 +4175,10 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B256" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C256">
         <v>4</v>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B257" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C257">
         <v>4</v>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B258" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C258">
         <v>4</v>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B259" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C259">
         <v>4</v>
@@ -4231,10 +4231,10 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B260" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C260">
         <v>4</v>
@@ -4245,10 +4245,10 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B261" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C261">
         <v>4.5</v>
@@ -4259,10 +4259,10 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B262" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C262">
         <v>4.5</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B263" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C263">
         <v>4.5</v>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B264" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C264">
         <v>4.5</v>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B265" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C265">
         <v>4.5</v>
@@ -4315,10 +4315,10 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B266" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C266">
         <v>4.5</v>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B267" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C267">
         <v>5</v>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B268" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C268">
         <v>5</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B269" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C269">
         <v>5</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B270" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C270">
         <v>5</v>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B271" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C271">
         <v>5</v>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B272" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C272">
         <v>5</v>
@@ -4413,10 +4413,10 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B273" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C273">
         <v>6</v>
@@ -4427,10 +4427,10 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B274" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C274">
         <v>6</v>
@@ -4441,10 +4441,10 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B275" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C275">
         <v>6</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B276" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C276">
         <v>6</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B277" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C277">
         <v>6</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B278" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C278">
         <v>6</v>
@@ -4497,10 +4497,10 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B279" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C279">
         <v>7</v>
@@ -4511,10 +4511,10 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B280" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C280">
         <v>7</v>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B281" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C281">
         <v>7</v>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B282" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C282">
         <v>7</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B283" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C283">
         <v>7</v>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B284" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C284">
         <v>7</v>
@@ -4581,10 +4581,10 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B285" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C285">
         <v>2</v>
@@ -4595,10 +4595,10 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B286" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C286">
         <v>2</v>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B287" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C287">
         <v>2</v>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B288" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C288">
         <v>2</v>
@@ -4637,10 +4637,10 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B289" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C289">
         <v>2.5</v>
@@ -4651,10 +4651,10 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B290" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C290">
         <v>2.5</v>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B291" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C291">
         <v>2.5</v>
@@ -4679,10 +4679,10 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B292" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C292">
         <v>2.5</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B293" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -4707,10 +4707,10 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B294" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -4721,10 +4721,10 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B295" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -4735,10 +4735,10 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B296" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -4749,10 +4749,10 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B297" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C297">
         <v>3.5</v>
@@ -4763,10 +4763,10 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B298" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C298">
         <v>3.5</v>
@@ -4777,10 +4777,10 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B299" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C299">
         <v>3.5</v>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B300" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C300">
         <v>3.5</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B301" t="s">
         <v>44</v>
-      </c>
-      <c r="B301" t="s">
-        <v>45</v>
       </c>
       <c r="C301">
         <v>3.2</v>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B302" t="s">
         <v>44</v>
-      </c>
-      <c r="B302" t="s">
-        <v>45</v>
       </c>
       <c r="C302">
         <v>3.2</v>
@@ -4833,10 +4833,10 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B303" t="s">
         <v>44</v>
-      </c>
-      <c r="B303" t="s">
-        <v>45</v>
       </c>
       <c r="C303">
         <v>3.2</v>
@@ -4847,10 +4847,10 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B304" t="s">
         <v>44</v>
-      </c>
-      <c r="B304" t="s">
-        <v>45</v>
       </c>
       <c r="C304">
         <v>3.2</v>
@@ -4861,10 +4861,10 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B305" t="s">
         <v>44</v>
-      </c>
-      <c r="B305" t="s">
-        <v>45</v>
       </c>
       <c r="C305">
         <v>3.2</v>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B306" t="s">
         <v>44</v>
-      </c>
-      <c r="B306" t="s">
-        <v>45</v>
       </c>
       <c r="C306">
         <v>3.2</v>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B307" t="s">
         <v>44</v>
-      </c>
-      <c r="B307" t="s">
-        <v>45</v>
       </c>
       <c r="C307">
         <v>3.2</v>
@@ -4903,10 +4903,10 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B308" t="s">
         <v>44</v>
-      </c>
-      <c r="B308" t="s">
-        <v>45</v>
       </c>
       <c r="C308">
         <v>3.5</v>
@@ -4917,10 +4917,10 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B309" t="s">
         <v>44</v>
-      </c>
-      <c r="B309" t="s">
-        <v>45</v>
       </c>
       <c r="C309">
         <v>3.5</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B310" t="s">
         <v>44</v>
-      </c>
-      <c r="B310" t="s">
-        <v>45</v>
       </c>
       <c r="C310">
         <v>3.5</v>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B311" t="s">
         <v>44</v>
-      </c>
-      <c r="B311" t="s">
-        <v>45</v>
       </c>
       <c r="C311">
         <v>3.5</v>
@@ -4959,10 +4959,10 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A312" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B312" t="s">
         <v>44</v>
-      </c>
-      <c r="B312" t="s">
-        <v>45</v>
       </c>
       <c r="C312">
         <v>3.5</v>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B313" t="s">
         <v>44</v>
-      </c>
-      <c r="B313" t="s">
-        <v>45</v>
       </c>
       <c r="C313">
         <v>3.5</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B314" t="s">
         <v>44</v>
-      </c>
-      <c r="B314" t="s">
-        <v>45</v>
       </c>
       <c r="C314">
         <v>3.5</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B315" t="s">
         <v>44</v>
-      </c>
-      <c r="B315" t="s">
-        <v>45</v>
       </c>
       <c r="C315">
         <v>4</v>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B316" t="s">
         <v>44</v>
-      </c>
-      <c r="B316" t="s">
-        <v>45</v>
       </c>
       <c r="C316">
         <v>4</v>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B317" t="s">
         <v>44</v>
-      </c>
-      <c r="B317" t="s">
-        <v>45</v>
       </c>
       <c r="C317">
         <v>4</v>
@@ -5043,10 +5043,10 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B318" t="s">
         <v>44</v>
-      </c>
-      <c r="B318" t="s">
-        <v>45</v>
       </c>
       <c r="C318">
         <v>4</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B319" t="s">
         <v>44</v>
-      </c>
-      <c r="B319" t="s">
-        <v>45</v>
       </c>
       <c r="C319">
         <v>4</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B320" t="s">
         <v>44</v>
-      </c>
-      <c r="B320" t="s">
-        <v>45</v>
       </c>
       <c r="C320">
         <v>4</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B321" t="s">
         <v>44</v>
-      </c>
-      <c r="B321" t="s">
-        <v>45</v>
       </c>
       <c r="C321">
         <v>4</v>
@@ -5099,10 +5099,10 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B322" t="s">
         <v>44</v>
-      </c>
-      <c r="B322" t="s">
-        <v>45</v>
       </c>
       <c r="C322">
         <v>4.5</v>
@@ -5113,10 +5113,10 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B323" t="s">
         <v>44</v>
-      </c>
-      <c r="B323" t="s">
-        <v>45</v>
       </c>
       <c r="C323">
         <v>4.5</v>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B324" t="s">
         <v>44</v>
-      </c>
-      <c r="B324" t="s">
-        <v>45</v>
       </c>
       <c r="C324">
         <v>4.5</v>
@@ -5141,10 +5141,10 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B325" t="s">
         <v>44</v>
-      </c>
-      <c r="B325" t="s">
-        <v>45</v>
       </c>
       <c r="C325">
         <v>4.5</v>
@@ -5155,10 +5155,10 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A326" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B326" t="s">
         <v>44</v>
-      </c>
-      <c r="B326" t="s">
-        <v>45</v>
       </c>
       <c r="C326">
         <v>4.5</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B327" t="s">
         <v>44</v>
-      </c>
-      <c r="B327" t="s">
-        <v>45</v>
       </c>
       <c r="C327">
         <v>4.5</v>
@@ -5183,10 +5183,10 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B328" t="s">
         <v>44</v>
-      </c>
-      <c r="B328" t="s">
-        <v>45</v>
       </c>
       <c r="C328">
         <v>4.5</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B329" t="s">
         <v>44</v>
-      </c>
-      <c r="B329" t="s">
-        <v>45</v>
       </c>
       <c r="C329">
         <v>5</v>
@@ -5211,10 +5211,10 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B330" t="s">
         <v>44</v>
-      </c>
-      <c r="B330" t="s">
-        <v>45</v>
       </c>
       <c r="C330">
         <v>5</v>
@@ -5225,10 +5225,10 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B331" t="s">
         <v>44</v>
-      </c>
-      <c r="B331" t="s">
-        <v>45</v>
       </c>
       <c r="C331">
         <v>5</v>
@@ -5239,10 +5239,10 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B332" t="s">
         <v>44</v>
-      </c>
-      <c r="B332" t="s">
-        <v>45</v>
       </c>
       <c r="C332">
         <v>5</v>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B333" t="s">
         <v>44</v>
-      </c>
-      <c r="B333" t="s">
-        <v>45</v>
       </c>
       <c r="C333">
         <v>5</v>
@@ -5267,10 +5267,10 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B334" t="s">
         <v>44</v>
-      </c>
-      <c r="B334" t="s">
-        <v>45</v>
       </c>
       <c r="C334">
         <v>5</v>
@@ -5281,10 +5281,10 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B335" t="s">
         <v>44</v>
-      </c>
-      <c r="B335" t="s">
-        <v>45</v>
       </c>
       <c r="C335">
         <v>5</v>
@@ -5295,10 +5295,10 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B336" t="s">
         <v>44</v>
-      </c>
-      <c r="B336" t="s">
-        <v>45</v>
       </c>
       <c r="C336">
         <v>6</v>
@@ -5309,10 +5309,10 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B337" t="s">
         <v>44</v>
-      </c>
-      <c r="B337" t="s">
-        <v>45</v>
       </c>
       <c r="C337">
         <v>6</v>
@@ -5323,10 +5323,10 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B338" t="s">
         <v>44</v>
-      </c>
-      <c r="B338" t="s">
-        <v>45</v>
       </c>
       <c r="C338">
         <v>6</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B339" t="s">
         <v>44</v>
-      </c>
-      <c r="B339" t="s">
-        <v>45</v>
       </c>
       <c r="C339">
         <v>6</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B340" t="s">
         <v>44</v>
-      </c>
-      <c r="B340" t="s">
-        <v>45</v>
       </c>
       <c r="C340">
         <v>6</v>
@@ -5365,10 +5365,10 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B341" t="s">
         <v>44</v>
-      </c>
-      <c r="B341" t="s">
-        <v>45</v>
       </c>
       <c r="C341">
         <v>6</v>
@@ -5379,10 +5379,10 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B342" t="s">
         <v>44</v>
-      </c>
-      <c r="B342" t="s">
-        <v>45</v>
       </c>
       <c r="C342">
         <v>6</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B343" t="s">
         <v>44</v>
-      </c>
-      <c r="B343" t="s">
-        <v>45</v>
       </c>
       <c r="C343">
         <v>7</v>
@@ -5407,10 +5407,10 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B344" t="s">
         <v>44</v>
-      </c>
-      <c r="B344" t="s">
-        <v>45</v>
       </c>
       <c r="C344">
         <v>7</v>
@@ -5421,10 +5421,10 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B345" t="s">
         <v>44</v>
-      </c>
-      <c r="B345" t="s">
-        <v>45</v>
       </c>
       <c r="C345">
         <v>7</v>
@@ -5435,10 +5435,10 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B346" t="s">
         <v>44</v>
-      </c>
-      <c r="B346" t="s">
-        <v>45</v>
       </c>
       <c r="C346">
         <v>7</v>
@@ -5449,10 +5449,10 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B347" t="s">
         <v>44</v>
-      </c>
-      <c r="B347" t="s">
-        <v>45</v>
       </c>
       <c r="C347">
         <v>7</v>
@@ -5463,10 +5463,10 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B348" t="s">
         <v>44</v>
-      </c>
-      <c r="B348" t="s">
-        <v>45</v>
       </c>
       <c r="C348">
         <v>7</v>
@@ -5477,10 +5477,10 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B349" t="s">
         <v>44</v>
-      </c>
-      <c r="B349" t="s">
-        <v>45</v>
       </c>
       <c r="C349">
         <v>7</v>
@@ -5491,10 +5491,10 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B350" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C350">
         <v>3.6</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B351" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C351">
         <v>4</v>
@@ -5519,10 +5519,10 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B352" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C352">
         <v>4.8</v>
@@ -5533,10 +5533,10 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B353" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C353">
         <v>3.3</v>
@@ -5547,10 +5547,10 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B354" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C354">
         <v>3.3</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B355" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C355">
         <v>3.3</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A356" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B356" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C356">
         <v>3.3</v>
@@ -5589,10 +5589,10 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A357" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B357" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C357">
         <v>3.75</v>
@@ -5603,10 +5603,10 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A358" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B358" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C358">
         <v>3.75</v>
@@ -5617,10 +5617,10 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B359" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C359">
         <v>3.75</v>
@@ -5631,10 +5631,10 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A360" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B360" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C360">
         <v>3.75</v>
@@ -5645,10 +5645,10 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B361" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C361">
         <v>4.2</v>
@@ -5659,10 +5659,10 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A362" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B362" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C362">
         <v>4.2</v>
@@ -5673,10 +5673,10 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B363" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C363">
         <v>4.2</v>
@@ -5687,10 +5687,10 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A364" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B364" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C364">
         <v>4.2</v>
@@ -5701,10 +5701,10 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B365" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C365">
         <v>4.2</v>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A366" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C366" s="2">
         <v>5</v>
@@ -5729,10 +5729,10 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C367" s="2">
         <v>5</v>
@@ -5743,10 +5743,10 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A368" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C368" s="2">
         <v>5</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C369" s="2">
         <v>5</v>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A370" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C370" s="2">
         <v>5</v>
@@ -5785,10 +5785,10 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A371" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B371" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C371">
         <v>3.75</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A372" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B372" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C372">
         <v>3.75</v>
@@ -5813,10 +5813,10 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B373" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C373">
         <v>5</v>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A374" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B374" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C374">
         <v>3.5</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A375" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B375" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C375">
         <v>4</v>
@@ -5855,10 +5855,10 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A376" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B376" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C376">
         <v>5</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B377" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C377">
         <v>3.5</v>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B378" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C378">
         <v>3.5</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B379" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C379">
         <v>3.5</v>
@@ -5911,10 +5911,10 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B380" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C380">
         <v>3.5</v>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B381" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C381">
         <v>4</v>
@@ -5939,10 +5939,10 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B382" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C382">
         <v>4</v>
@@ -5953,10 +5953,10 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B383" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C383">
         <v>4</v>
@@ -5967,10 +5967,10 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B384" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C384">
         <v>4</v>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B385" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C385">
         <v>4</v>
@@ -5995,10 +5995,10 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B386" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C386">
         <v>4.5</v>
@@ -6009,10 +6009,10 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B387" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C387">
         <v>4.5</v>
@@ -6023,10 +6023,10 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B388" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C388">
         <v>4.5</v>
@@ -6037,10 +6037,10 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B389" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C389">
         <v>4.5</v>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B390" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C390">
         <v>4.5</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B391" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C391">
         <v>5</v>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B392" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C392">
         <v>5</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B393" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C393">
         <v>5</v>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B394" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C394">
         <v>5</v>
@@ -6121,10 +6121,10 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B395" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C395">
         <v>5</v>
@@ -6135,10 +6135,10 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B396" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C396">
         <v>5.5</v>
@@ -6149,10 +6149,10 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B397" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C397">
         <v>5.5</v>
@@ -6163,10 +6163,10 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B398" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C398">
         <v>5.5</v>
@@ -6177,10 +6177,10 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B399" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C399">
         <v>5.5</v>
@@ -6191,10 +6191,10 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B400" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C400">
         <v>5.5</v>
@@ -6205,10 +6205,10 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B401" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C401">
         <v>6</v>
@@ -6219,10 +6219,10 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B402" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C402">
         <v>6</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B403" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C403">
         <v>6</v>
@@ -6247,10 +6247,10 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B404" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C404">
         <v>6</v>
@@ -6261,10 +6261,10 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B405" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C405">
         <v>6</v>
@@ -6275,10 +6275,10 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B406" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C406">
         <v>3.5</v>
@@ -6289,10 +6289,10 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B407" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C407">
         <v>3.5</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B408" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C408">
         <v>3.5</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B409" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C409">
         <v>3.5</v>
@@ -6331,10 +6331,10 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
+        <v>56</v>
+      </c>
+      <c r="B410" t="s">
         <v>58</v>
-      </c>
-      <c r="B410" t="s">
-        <v>60</v>
       </c>
       <c r="C410">
         <v>4</v>
@@ -6345,10 +6345,10 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
+        <v>56</v>
+      </c>
+      <c r="B411" t="s">
         <v>58</v>
-      </c>
-      <c r="B411" t="s">
-        <v>60</v>
       </c>
       <c r="C411">
         <v>4</v>
@@ -6359,10 +6359,10 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
+        <v>56</v>
+      </c>
+      <c r="B412" t="s">
         <v>58</v>
-      </c>
-      <c r="B412" t="s">
-        <v>60</v>
       </c>
       <c r="C412">
         <v>4</v>
@@ -6373,10 +6373,10 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
+        <v>56</v>
+      </c>
+      <c r="B413" t="s">
         <v>58</v>
-      </c>
-      <c r="B413" t="s">
-        <v>60</v>
       </c>
       <c r="C413">
         <v>4</v>
@@ -6387,10 +6387,10 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
+        <v>56</v>
+      </c>
+      <c r="B414" t="s">
         <v>58</v>
-      </c>
-      <c r="B414" t="s">
-        <v>60</v>
       </c>
       <c r="C414">
         <v>4</v>
@@ -6401,10 +6401,10 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
+        <v>56</v>
+      </c>
+      <c r="B415" t="s">
         <v>58</v>
-      </c>
-      <c r="B415" t="s">
-        <v>60</v>
       </c>
       <c r="C415">
         <v>4.5</v>
@@ -6415,10 +6415,10 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
+        <v>56</v>
+      </c>
+      <c r="B416" t="s">
         <v>58</v>
-      </c>
-      <c r="B416" t="s">
-        <v>60</v>
       </c>
       <c r="C416">
         <v>4.5</v>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
+        <v>56</v>
+      </c>
+      <c r="B417" t="s">
         <v>58</v>
-      </c>
-      <c r="B417" t="s">
-        <v>60</v>
       </c>
       <c r="C417">
         <v>4.5</v>
@@ -6443,10 +6443,10 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
+        <v>56</v>
+      </c>
+      <c r="B418" t="s">
         <v>58</v>
-      </c>
-      <c r="B418" t="s">
-        <v>60</v>
       </c>
       <c r="C418">
         <v>4.5</v>
@@ -6457,10 +6457,10 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
+        <v>56</v>
+      </c>
+      <c r="B419" t="s">
         <v>58</v>
-      </c>
-      <c r="B419" t="s">
-        <v>60</v>
       </c>
       <c r="C419">
         <v>4.5</v>
@@ -6471,10 +6471,10 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
+        <v>56</v>
+      </c>
+      <c r="B420" t="s">
         <v>58</v>
-      </c>
-      <c r="B420" t="s">
-        <v>60</v>
       </c>
       <c r="C420">
         <v>5</v>
@@ -6485,10 +6485,10 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
+        <v>56</v>
+      </c>
+      <c r="B421" t="s">
         <v>58</v>
-      </c>
-      <c r="B421" t="s">
-        <v>60</v>
       </c>
       <c r="C421">
         <v>5</v>
@@ -6499,10 +6499,10 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
+        <v>56</v>
+      </c>
+      <c r="B422" t="s">
         <v>58</v>
-      </c>
-      <c r="B422" t="s">
-        <v>60</v>
       </c>
       <c r="C422">
         <v>5</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
+        <v>56</v>
+      </c>
+      <c r="B423" t="s">
         <v>58</v>
-      </c>
-      <c r="B423" t="s">
-        <v>60</v>
       </c>
       <c r="C423">
         <v>5</v>
@@ -6527,10 +6527,10 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
+        <v>56</v>
+      </c>
+      <c r="B424" t="s">
         <v>58</v>
-      </c>
-      <c r="B424" t="s">
-        <v>60</v>
       </c>
       <c r="C424">
         <v>5</v>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B425" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C425">
         <v>5</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B426" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C426">
         <v>5</v>
@@ -6569,10 +6569,10 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B427" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C427">
         <v>5</v>
@@ -6583,10 +6583,10 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B428" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C428">
         <v>5</v>
@@ -6597,10 +6597,10 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B429" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C429">
         <v>5</v>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B430" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C430">
         <v>5.5</v>
@@ -6625,10 +6625,10 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B431" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C431">
         <v>5.5</v>
@@ -6639,10 +6639,10 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B432" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C432">
         <v>5.5</v>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B433" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C433">
         <v>5.5</v>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B434" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C434">
         <v>5.5</v>
@@ -6681,10 +6681,10 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B435" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C435">
         <v>6</v>
@@ -6695,10 +6695,10 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B436" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C436">
         <v>6</v>
@@ -6709,10 +6709,10 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B437" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C437">
         <v>6</v>
@@ -6723,10 +6723,10 @@
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B438" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C438">
         <v>6</v>
@@ -6737,10 +6737,10 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B439" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C439">
         <v>6</v>
